--- a/光伏配储项目/电价数据/2026/钱岗站.xlsx
+++ b/光伏配储项目/电价数据/2026/钱岗站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.51181</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.39275</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.75825</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.5749</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5993200000000001</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.51776</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.5163</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43767</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45452</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44552</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42386</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42318</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40909</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39872</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40154</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38492</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.4026</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42321</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41261</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35466</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39152</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38501</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41699</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.3922</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.4208</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41395</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42395</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41344</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44465</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.36954</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.3152</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29501</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.31618</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.31812</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32457</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.1283</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.10438</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.11868</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.10821</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.13088</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.04907</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.1079</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.15732</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.19988</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.27732</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.09129999999999999</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.26647</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.10115</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.04475</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.15246</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21672</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25495</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.42448</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.23934</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.17897</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.02248</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.5292100000000001</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.14307</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.3951</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.28345</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.42362</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.38655</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.21277</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.3346</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.64136</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.55983</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.56556</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.33298</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.40955</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.6165900000000001</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.46117</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44671</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.46203</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.57789</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.47428</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.63549</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.8210499999999999</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.63978</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.6523300000000001</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.79473</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.15193</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.42926</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.68547</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.60041</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.8225800000000001</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.6648999999999999</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.68062</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.65126</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.6211</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.47738</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48128</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.39773</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41642</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42613</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.70788</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.80371</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.55305</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.8660599999999999</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53651</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5180399999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5087900000000001</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48724</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40239</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46935</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38066</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37989</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39054</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33677</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37004</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36036</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37454</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.3747</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35867</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37968</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41833</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.49781</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.59982</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.75283</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42831</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.3852</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.44153</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33689</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.43217</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.52146</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.17125</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29697</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.37164</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.0615</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.35582</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.35549</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.34251</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.36877</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.35289</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.50285</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.7673</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.17029</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.33505</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.36647</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.38066</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.3862</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.41793</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.7971900000000001</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.5391</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.34973</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.13132</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28337</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.38723</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.31424</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.34796</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.51403</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.34284</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.26547</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.35398</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.34864</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.39445</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.10702</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.42647</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.26566</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.36305</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.43162</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.36787</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.6403</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.78589</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.62176</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.22101</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.7900700000000001</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.73946</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.66599</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.6052799999999999</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.77452</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.56814</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.45548</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.08156</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.39309</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.47045</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.67587</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44342</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43684</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.42125</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.34897</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.38065</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35824</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33469</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51751</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.3847</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.52489</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.41788</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38202</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40425</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.41478</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38886</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36751</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43699</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45359</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37065</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.3964</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.37169</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.3723399999999999</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35612</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36162</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36709</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35929</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38517</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.3964</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47377</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45349</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44775</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.40069</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35302</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37114</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.46235</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.37618</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.37873</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.4794</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.27101</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31828</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.30548</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34494</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.47608</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.4070299999999999</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.50841</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.48632</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.42272</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.29369</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.16379</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.27885</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.32879</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.2825299999999999</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29319</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.34064</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29879</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.27834</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.39813</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.4017</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.52925</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.42928</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.19501</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.5327999999999999</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.5805</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.89846</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.39148</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.34909</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.36754</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.56328</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.63936</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.7094400000000001</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.57713</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.33485</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.49704</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.44317</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.52654</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.42463</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.48357</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.45142</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.47307</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>1.45882</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.41686</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.38928</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.44058</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.41807</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.40535</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.41005</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.3688</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34908</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34231</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31916</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.39915</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.43467</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.36396</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.33326</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.32666</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.34586</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.31638</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.32166</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46069</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.31857</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.32115</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.32977</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.32705</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.30218</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.30761</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.30365</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.29574</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.30415</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.32721</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35377</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.35399</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38929</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.3365</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.34091</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.31505</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.33968</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.29186</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.35318</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.37076</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.38346</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.33641</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.33649</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30986</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.34573</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.23411</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.44681</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.36673</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.0974</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.09742000000000001</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.17421</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.30473</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.28225</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.1785</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.21901</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.5108199999999999</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.06709999999999999</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.1199</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.22886</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.24288</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.37356</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.33832</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.28524</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.21673</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.23649</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.20029</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.26484</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.12487</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>1.18739</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.2686</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.29806</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33644</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.30823</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33823</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.35131</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.39001</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.4442</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.67187</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.47231</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.42735</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.36044</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.34237</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.35216</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.35498</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.32391</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.33321</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.30171</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31541</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32522</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.2962</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.3117200000000001</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31706</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.30248</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29917</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.30377</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.41566</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38187</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35628</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30057</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31126</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31044</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30709</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.28912</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.3055</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.3058</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.2932</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.28965</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.28965</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.28955</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29792</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29171</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29472</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30549</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33278</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27835</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.25901</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.04769</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.03896</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.04861</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.04969</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04452</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04083</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.04543999999999999</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04245</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.0362</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04715999999999999</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04629999999999999</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04972</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.0476</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04636999999999999</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04669</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04915</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.0447</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04712</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04378</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04202</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04487</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04566</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21832</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.03937</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.04525</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05511</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.04972</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.04789</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.01271</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.15534</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.0555</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29025</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29371</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29368</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33614</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38802</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39239</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38782</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37769</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40041</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39997</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41123</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.4673</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.3962</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39972</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41642</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35491</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35804</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34517</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35533</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35061</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36796</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.39945</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.4447</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42201</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42186</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35967</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35846</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35796</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33188</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.3089</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32258</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.3472</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31399</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33439</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33814</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35179</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.3414</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.3156600000000001</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10255</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04371</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04543</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04563</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04674</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.09795000000000001</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.00466</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04524</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04399</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04578</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04564</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04562</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04366</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04553</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04703</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.045</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04365</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04952</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04463</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04992</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04954</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04733</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04775</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19997</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14285</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29016</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29486</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30474</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29514</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29312</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29364</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29259</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29701</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.2909</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.2951</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26891</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29396</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29819</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30865</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30392</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30222</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31446</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34768</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34435</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36624</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36479</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33536</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33016</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31745</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40423</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34978</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32071</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.3071</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31471</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30141</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28121</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29435</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29079</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28808</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28093</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27123</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28112</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17242</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15866</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17095</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14772</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15946</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15861</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23617</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21403</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22657</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.2688</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28576</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29083</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31941</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.2908</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28093</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28111</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28052</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27171</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28102</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31025</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30502</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35916</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31653</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29831</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38389</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42873</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45706</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41889</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41576</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40279</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30013</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30101</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29945</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30007</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15635</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29557</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31111</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31355</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30078</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38565</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50773</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7909400000000001</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220800000000001</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40009</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49804</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78108</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92052</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49465</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91525</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8653200000000001</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29794</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.89037</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63222</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18994</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8701599999999999</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.53916</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33371</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03492</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5336000000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79331</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.52935</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7753300000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7794</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87706</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87509</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49533</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.40083</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.40276</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.45247</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20986</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87899</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.5511200000000001</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6247</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5390499999999999</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49855</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45621</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42464</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43769</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45011</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38893</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45277</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35206</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39996</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36516</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38575</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41457</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43351</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34373</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39017</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.34098</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33444</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34639</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40285</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45077</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35379</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40008</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.39947</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58539</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42692</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5956</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.6014700000000001</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66174</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47364</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41905</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.58231</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45175</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8780399999999999</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.62802</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.87502</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.85758</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.86511</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34857</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44299</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32736</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30684</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.34235</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.46063</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29428</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.29388</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31245</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35699</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33283</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.3212</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33718</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30633</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31988</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31518</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29438</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31215</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31362</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31215</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31421</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30987</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31482</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32301</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34039</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33785</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33034</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.3371499999999999</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.4093</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.4119</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45138</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41424</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39096</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35325</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.91528</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46342</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.34936</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.4575</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.37931</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40918</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.35799</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34595</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34679</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38898</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32273</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.39935</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.4987200000000001</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35672</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38702</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34316</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35484</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37015</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.3576</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31355</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33247</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33743</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34915</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31498</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29073</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30676</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.29113</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30058</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16656</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30861</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.33026</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29697</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26261</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19898</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27713</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19048</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27818</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31132</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35664</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35257</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31281</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.3114</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31977</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30426</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29422</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31425</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.28922</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30744</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29006</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34808</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25567</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32172</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.27572</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33861</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27648</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.3098</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31812</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38524</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.33339</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43143</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.27681</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42314</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35065</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44754</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.41976</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35872</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40098</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.39967</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5945199999999999</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.34906</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.88975</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.32744</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.13599</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.69723</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7872</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6427</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.57639</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.44827</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.44963</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.49959</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4392</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43635</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41441</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41233</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42252</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.49862</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41234</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43342</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41179</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43342</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38994</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42665</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.44881</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39578</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4229</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.4327</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41234</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41238</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.39918</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42215</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3944</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40121</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49175</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36189</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34519</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.2967</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36982</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.37445</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.31368</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.3667</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.3138</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.36265</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.95368</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.6177699999999999</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.22988</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>1.19346</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25038</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.99591</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.69973</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.40175</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.32111</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.31193</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.67415</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.38189</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.40322</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.40975</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.3822</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.44126</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.37406</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.37974</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31935</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.37058</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1.48927</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31576</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.35297</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34078</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.40811</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.39968</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.38749</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>1.35087</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36282</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.4049</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36235</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.5746</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46134</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.74315</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46329</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43624</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37445</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.41916</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.3851</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36817</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32837</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32327</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42085</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34266</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33753</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32741</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30857</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32458</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31477</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30919</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32404</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.3102</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31584</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.31868</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.38891</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32148</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39726</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37254</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34836</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35309</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33324</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>1.43113</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.33368</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.90606</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.3614</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.34351</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.16364</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.1682</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>1.14164</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.17509</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.95504</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.94637</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14982</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.15773</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.15002</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.1569</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.27988</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.28801</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.30717</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.15717</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.19766</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.34903</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.41083</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.15687</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.16204</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.31287</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.34418</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.35622</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>1.31858</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.36108</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.35623</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.39294</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37855</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34616</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.37669</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38348</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.4476</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39835</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.37154</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40006</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39589</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.43911</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43761</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43696</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44184</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44302</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40146</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38954</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39673</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3906</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35845</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34665</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34818</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33863</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.53501</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46622</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42188</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41404</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.36929</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.3794</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.37844</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39146</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37892</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36947</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37948</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39019</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36952</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.3794</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34667</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35459</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33967</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34464</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33967</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34428</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35395</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36946</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.37942</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35944</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.3276</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.3481</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29874</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31449</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31404</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30838</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29546</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28241</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.27212</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26698</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.20331</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30998</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.25032</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24394</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27062</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30081</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28856</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31799</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31754</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31415</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31453</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.2945</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.2874</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24256</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31583</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30792</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30689</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28621</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31571</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33332</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33894</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33553</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34558</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.34422</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.34857</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.31574</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.34492</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.24494</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.31729</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38065</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35759</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35481</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.38574</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36678</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36939</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.37932</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.37977</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38445</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.3596</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36566</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41783</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37022</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39099</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38005</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35193</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35962</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35091</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34118</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34686</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34251</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33975</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33004</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34058</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34327</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36186</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.30997</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33856</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32465</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33461</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.40906</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.36101</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.37633</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.40445</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.33515</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.43981</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.30491</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.3027</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.46886</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.10464</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.2812</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24929</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.40713</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.12096</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.2542</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.25724</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.30951</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.31017</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.30373</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.30274</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.36171</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.42883</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.35278</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.35684</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.36056</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.32376</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.37324</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32526</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.34505</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.34446</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.44139</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.42797</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.69936</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.37036</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.37902</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.3173</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.5267999999999999</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.24492</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.37855</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.3129</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32651</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.32407</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.29949</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30509</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.29754</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.28235</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30502</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.36505</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33236</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.32914</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32391</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.3236</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.31729</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32334</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.3266</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32763</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32672</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32378</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.3297</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31961</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32585</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33403</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34523</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.33933</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33372</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33731</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32917</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32009</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32175</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32467</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31677</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.3409</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.30185</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34444</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34429</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31424</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.33429</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28819</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31751</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32084</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32524</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32768</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.37292</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.3269</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31947</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32009</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31527</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>1.31566</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.32378</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36914</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34565</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33493</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34967</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.35923</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33315</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32963</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34344</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.36679</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.35989</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.3518</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.35757</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.35299</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.36313</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35816</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.37807</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38492</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37133</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.39573</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35472</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37975</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36212</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34885</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34938</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34958</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35149</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35059</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34633</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35712</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34707</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34681</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34925</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33651</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33979</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36903</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32413</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34923</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33644</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34479</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33566</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34928</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34927</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33629</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.33958</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32797</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34826</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33614</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30751</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32906</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32597</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31657</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.3166</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36845</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32378</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31904</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.32275</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32366</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32277</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32226</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32966</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32949</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33227</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34487</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.3585</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.33709</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.3537</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35356</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35437</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36604</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34555</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35843</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35853</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38221</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37844</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38044</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38431</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42443</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41123</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37948</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.3762</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65691</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.7664099999999999</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.45182</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.29193</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45682</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39465</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35352</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34431</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41107</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37042</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36167</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35886</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35854</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.3617</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35866</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35253</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35594</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35882</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35946</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.36457</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37006</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35848</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.3788</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36554</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35617</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35076</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35145</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35782</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31867</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33415</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32639</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.28198</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.21246</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31277</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28512</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.2847</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.20038</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.26036</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.28074</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.32074</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28019</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.21921</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.2686</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28603</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27976</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.29036</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.29343</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30651</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.3332</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32356</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.18719</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.44505</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32796</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33513</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.33955</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.35873</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.44922</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.43082</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.39082</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.46654</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.44956</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.36503</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32521</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43608</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.42105</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.64103</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.6079600000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.59477</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.46483</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.66553</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.47122</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.82267</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.48378</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.6149600000000001</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40622</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37296</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.47505</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.42939</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41871</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37804</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37449</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36676</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.35966</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34238</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.4889</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.53642</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.48478</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.49157</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41634</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39712</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40246</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.40957</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40719</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.4155</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39451</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.40974</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40746</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39315</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38715</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41731</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38689</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41575</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38929</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39889</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39902</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41135</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.39889</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.44818</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44758</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.55692</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.44856</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.7447699999999999</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.4498</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.46772</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.37256</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38487</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.41602</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.44724</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.42108</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.48684</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.45868</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.30171</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.37444</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.40303</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.40124</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.41561</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.33232</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.34702</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.29097</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.33513</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.34737</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.35161</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.38181</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.6508200000000001</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.37269</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.34812</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.26807</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.36433</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.34758</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.32735</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.35315</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37211</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35874</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.37247</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.36151</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.38752</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.41722</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.4393</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.49222</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43882</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.50831</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.51201</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.54627</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.69884</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.7302999999999999</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.50603</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.64824</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.8100700000000001</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.59051</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.52663</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.8385499999999999</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7782</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.62737</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.67733</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.44853</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47754</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.48366</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.4761</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.47006</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41687</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5555599999999999</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.4289</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44106</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45568</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.4355</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42482</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44545</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41683</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39863</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45453</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39686</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40412</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38578</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37765</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37269</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36554</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37283</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37025</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35963</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36554</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.3857</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.38917</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3795</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36583</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35488</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37942</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39935</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.37061</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.3868</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39929</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38626</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36889</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34415</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.35324</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.38436</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.20693</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.39121</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.35706</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.35034</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.04279</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.3712</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.4033</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.35424</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.4496</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.3905</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46117</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.32868</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31202</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.1137</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.29674</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29385</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.34848</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34771</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.3643</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.37847</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37263</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41688</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36968</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.43239</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.40219</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.4165</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38572</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.3805</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38494</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39007</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40811</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40866</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34518</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.37095</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37617</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39661</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37893</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35477</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.3988</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.37843</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37427</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.35834</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39396</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37911</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36454</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.32847</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44356</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36221</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39591</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35755</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37775</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.34863</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37513</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35578</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35545</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35208</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35581</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.3448</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34767</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.32963</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33825</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.33887</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33362</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.3386</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34358</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.32735</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.32639</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31678</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.30712</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30315</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.31225</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.27844</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.31763</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31341</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30713</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22538</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28679</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23055</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.28772</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25006</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.25905</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13907</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.2943</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29798</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.31691</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.24995</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04291</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.2504</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.29315</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.17107</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18319</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.27776</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.3096</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.31668</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.22996</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.25102</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26596</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23383</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27628</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28411</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28505</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30906</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.37498</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34432</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31032</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35595</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35798</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.38189</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.37009</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36963</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37132</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34466</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36473</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.38057</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36245</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36671</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.35845</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34721</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.34667</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.34903</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="C136" t="n">
+        <v>1.32567</v>
+      </c>
+      <c r="D136" t="n">
+        <v>1.33695</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.3378</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.32694</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31723</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31727</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30556</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30772</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.3127200000000001</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.30956</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.30633</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.30717</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.3072</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.30735</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30322</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30322</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30562</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30241</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30322</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30366</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.30886</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.30741</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.28718</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.24783</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.23284</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.16044</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.19834</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.23444</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01822</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00098</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.03237</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04906</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.10955</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.02091</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03904</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04908</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01275</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.03648</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.03279</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04719</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02438</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02196</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04912</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.20302</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04908</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04911</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04888</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00114</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.30699</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04915</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04893</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.0491</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.03495</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04907</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04883</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.0435</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.17684</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.18907</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.23009</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28034</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.2589</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.26064</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.25624</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.26408</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.27804</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.29934</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.2862</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.28451</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.27867</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30661</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.29315</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.30467</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.28288</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.3032</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.28239</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.29829</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.2895</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.41053</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.32322</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.32975</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.30571</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.28707</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.28369</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.27892</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.27676</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.32862</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.11364</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29803</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.55301</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.13299</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.29983</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.27866</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.24489</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.29138</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.30137</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.28741</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.25784</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.23444</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.22219</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.25207</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.24203</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.20492</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.22989</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.23516</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.27169</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.25707</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.25545</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.23669</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.29388</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.26272</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.29734</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.34882</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.29461</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.26795</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.26974</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.21177</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.13028</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.61848</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.58646</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.6319600000000001</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.56979</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>1.14723</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.30552</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>1.12004</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>1.23234</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>1.17335</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.09645999999999999</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.10719</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.05625</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.22313</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.08987000000000001</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.30701</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.00086</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.01814</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.08011</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.16346</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.02905</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.09863</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.10755</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.1293</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.02676</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.08005</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.09275</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.09147</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.13619</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>1.25877</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29603</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.27943</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32025</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>1.3331</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>1.33292</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>1.32844</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>1.33848</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33929</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.3314</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.3585</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.35839</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.3748</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.33716</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.3874</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.37727</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.44859</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.37334</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.37455</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.36183</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.36326</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>1.35449</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>1.36989</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>1.35789</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1.36741</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.37327</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.33193</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.32696</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32905</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33797</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32273</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="C138" t="n">
+        <v>1.35437</v>
+      </c>
+      <c r="D138" t="n">
+        <v>1.37148</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.39274</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.34409</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.32936</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33003</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32774</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34071</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33738</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33429</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32685</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="R138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32239</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.31968</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.30549</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.31542</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.31406</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.31868</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.55076</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.5497000000000001</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.4079100000000001</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.42943</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.34539</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.38887</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.4495</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.36622</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.48445</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.39262</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.44994</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.38433</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.37798</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.36776</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.44652</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31446</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.33162</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31208</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14246</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27884</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27024</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30557</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.33037</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.33019</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32141</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.27339</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31241</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29221</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31326</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32254</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33252</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34635</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.3479100000000001</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34925</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35628</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.36172</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33582</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.35086</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36599</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37658</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.30045</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.50639</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35229</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35703</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.38746</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.36087</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35497</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36974</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.30869</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.32854</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.32844</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.27594</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31518</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33867</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34465</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.3023</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34829</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33429</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.31713</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.31784</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34582</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33052</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.33944</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32247</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36834</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35428</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36869</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.37292</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35373</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.37768</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.64585</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.33816</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.60458</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.34785</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.50575</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.37871</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36728</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.36306</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.31059</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.35338</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.43207</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31254</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.34905</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26331</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34853</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35229</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.28482</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.28778</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.34058</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.34042</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.3474100000000001</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.36582</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.36855</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.41191</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39924</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.49322</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.50376</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.4670899999999999</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.49002</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.42384</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.5764900000000001</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.41605</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.3996</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.48757</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.35469</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.31731</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.35824</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.35485</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.38313</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41492</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.36734</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.37869</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.36867</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45804</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40107</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.3847</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.40463</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.3817</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.35365</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37232</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36389</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36835</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34694</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.48078</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40123</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.4011</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39201</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.35957</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37465</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37387</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37801</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37638</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36835</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36653</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36103</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32711</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35578</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.34971</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34675</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37077</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39873</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37545</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.3716</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36179</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.36767</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.41258</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.41881</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.38821</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.37015</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.46154</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.40174</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.38017</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.28676</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35734</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.37194</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.27677</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.38596</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.36749</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29477</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.31621</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33967</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.31977</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.34223</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.35258</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.34534</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.35737</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.30759</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.36044</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.35853</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.39421</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.38575</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.39151</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37345</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.39262</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.46134</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.40189</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.44186</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.41677</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.43624</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.5140800000000001</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5850299999999999</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.5896699999999999</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.37999</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.40793</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.5182599999999999</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.50903</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.54906</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.46543</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.37457</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.51146</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.39773</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.73497</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.89904</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.59174</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.58977</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39826</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.4441000000000001</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39896</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37461</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37686</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36746</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37294</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.25354</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36925</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36549</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34493</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32113</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33153</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34058</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33623</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33434</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33817</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33577</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.31687</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31484</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.31761</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31692</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.30713</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.30675</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36838</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.30881</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30309</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.29796</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.29394</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.29336</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.31446</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.31581</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.21887</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.32566</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.31286</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.16897</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.28485</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.15287</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.07257999999999999</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.4092</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.36657</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.20998</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.04246</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.21076</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.16884</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.01114</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.31491</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26476</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.16578</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.06282</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.06178</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.07889</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.16777</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.08431999999999999</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.0611</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.17549</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.15666</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.4992799999999999</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.28371</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.31505</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.38187</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.43888</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.38019</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.35571</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.36289</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.38678</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36984</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.24089</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.34787</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36283</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.30589</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.37629</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.42429</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.37737</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.40042</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.41078</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38444</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39926</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.42679</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.38788</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.38529</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.41915</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37278</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.43462</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38013</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37203</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.35427</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.35718</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.35657</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.33293</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.86211</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.36602</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.46676</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.41823</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.39399</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33308</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.37665</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.38704</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.34615</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.36243</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.34668</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.34714</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.36985</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38432</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.35558</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.34707</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.35711</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.35379</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35408</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35453</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38596</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.33508</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.34682</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33362</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.30065</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.31805</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.30651</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.32389</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.31335</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.29743</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.25149</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.24629</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.26938</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.24293</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.11343</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.07008</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.07479999999999999</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.1011</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.13527</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.29565</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.13107</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00354</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01952</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.0493</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.02094</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.02713</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.07285</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.21103</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.30147</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.0492</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.23579</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.04266</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.22134</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.28548</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.32557</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.40961</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.33266</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.50087</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.40337</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.39727</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36212</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37305</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39096</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36477</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34175</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.39916</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.5880299999999999</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.37593</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.36902</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.36316</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.36687</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.37118</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.35961</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.37982</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.34039</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.41368</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.39673</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.36963</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38657</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.35714</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.35642</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.34927</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.3581</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.33359</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.6232000000000001</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36755</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.36893</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35342</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.34737</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.45712</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39099</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37092</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34345</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.3415899999999999</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.32291</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.3319</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32402</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32657</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.34219</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33255</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33071</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.34418</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33169</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.30772</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.27837</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.2555</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.22802</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.1427</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.20329</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.22682</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.22805</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.14833</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>-0.00312</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04729</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04740999999999999</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.04679999999999999</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04761</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04749</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.04188</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.07784000000000001</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03043</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.06269</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.09593</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.16803</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.19321</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.1191</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.2505</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.22656</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.12273</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.05567</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.26056</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.14425</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.11626</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.23476</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.18249</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.23266</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.23997</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.20087</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.24115</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.27064</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.27239</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.2966</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.30231</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.30482</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.30954</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.33019</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.3378</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.35828</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.34922</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.37699</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35103</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.36113</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.36092</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.35955</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.38974</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.39472</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.46787</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.38469</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.38309</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.3784</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.3881</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.36573</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.37549</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38123</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.36414</v>
       </c>
     </row>
   </sheetData>
